--- a/GO_LIST_2010.xlsx
+++ b/GO_LIST_2010.xlsx
@@ -884,10 +884,10 @@
         <v>2221608</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>1010580</v>
+        <v>1114900</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>0.5451132693076366</v>
+        <v>0.4981562903986662</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>0.25</v>
@@ -896,17 +896,21 @@
         <v>1666206</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>517711.0334465753</v>
+        <v>426123.7896109588</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>0.5263690414521072</v>
+        <v>0.4774771362138123</v>
       </c>
       <c r="P6" s="5" t="inlineStr">
         <is>
-          <t>15 000 шт × 9.9 ₽ (натрия цитратом); 200 шт × 9.9 ₽ (лития гепарином); 24 000 шт × 9.9 ₽ (активатором сверты); 22 000 шт × 9.9 ₽ (K2ЭДТА); доставка 196 800 ₽</t>
-        </is>
-      </c>
-      <c r="Q6" s="5" t="inlineStr"/>
+          <t>15 000 шт × 10.0 ₽ (натрия цитратом); 200 шт × 13.5 ₽ (лития гепарином); 24 000 шт × 15.0 ₽ (активатором свертывани); 22 000 шт × 10.0 ₽ (K2ЭДТА); доплата за дальнюю доставку 82 200 ₽ (МиниМед  прайс ©2026  РФ — импорт запрещён ПП 1875)</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>активатор посчитан с гелем (15 ₽) — с запасом; нужны РУ и реестр РФ (импорт запрещён)</t>
+        </is>
+      </c>
       <c r="R6" s="10" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0338200002226000430</t>
@@ -1038,10 +1042,10 @@
         <v>671066</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>429852.5</v>
+        <v>399300</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>0.3594482509917057</v>
+        <v>0.4049765596826541</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>0.1</v>
@@ -1050,14 +1054,14 @@
         <v>603959.4</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>131871.6246416439</v>
+        <v>158695.0455320548</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>0.3330534429514832</v>
+        <v>0.3804578076678099</v>
       </c>
       <c r="P8" s="5" t="inlineStr">
         <is>
-          <t>121 шт × 3 500 ₽ + доставка 35 ₽/кг</t>
+          <t>121 шт × 3 300 ₽ с доставкой (Стоик «Горка СТ» опт 3 139 ₽  мин. заказ 50 тыс.)</t>
         </is>
       </c>
       <c r="Q8" s="5" t="inlineStr"/>
@@ -1115,10 +1119,10 @@
         <v>863700</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>510000</v>
+        <v>500000</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>0.4095171934699549</v>
+        <v>0.421095287715642</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>0.25</v>
@@ -1126,18 +1130,22 @@
       <c r="M9" s="7" t="n">
         <v>647775</v>
       </c>
-      <c r="N9" s="7" t="n">
-        <v>98451.82520547944</v>
+      <c r="N9" s="9" t="n">
+        <v>107231.277260274</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>0.3851855444602657</v>
+        <v>0.3972407298630055</v>
       </c>
       <c r="P9" s="5" t="inlineStr">
         <is>
-          <t>30 000 шт × 9.9 ₽ (активатором сверты); 20 000 шт × 9.9 ₽ (K3ЭДТА); доставка 15 000 ₽</t>
-        </is>
-      </c>
-      <c r="Q9" s="5" t="inlineStr"/>
+          <t>30 000 шт × 10.0 ₽ (активатором свертывани); 20 000 шт × 10.0 ₽ (K3ЭДТА); доплата за дальнюю доставку 0 ₽ (МиниМед  прайс ©2026  РФ — импорт запрещён ПП 1875)</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>посчитано для активатора БЕЗ геля (10 ₽); если в ТЗ с гелем (15 ₽) — при −25% убыток ~29 тыс., подавать не ниже −20%</t>
+        </is>
+      </c>
       <c r="R9" s="10" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0372200263426001564</t>
@@ -1236,74 +1244,74 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>21.10.2026 09:00</t>
+          <t>26.10.2026 08:00</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Спецодежда</t>
+          <t>Пробирки</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>32616452870</t>
+          <t>0325300007726000124</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>ГУП РБ «Салаватводоканал» (2-й лот)</t>
+          <t>ГБУЗ АО «Городская поликлиника №5», Астрахань</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Костюмы от электродуги, термобельё, обувь, СИЗ (9 позиций)</t>
+          <t>Пробирки вакуумные K3ЭДТА, 30 000 шт</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ · запрос котировок (МСП)</t>
+          <t>44-ФЗ · запрос котировок</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>Росэлторг (corp)</t>
+          <t>Росэлторг</t>
         </is>
       </c>
       <c r="I11" s="7" t="n">
-        <v>700000</v>
+        <v>496200</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>558596</v>
+        <v>300000</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>0.2020057142857142</v>
+        <v>0.3954050785973398</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>630000</v>
+        <v>372150</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>40799.32</v>
+        <v>50413.31835616439</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>0.169123271889401</v>
+        <v>0.3704919206562006</v>
       </c>
       <c r="P11" s="5" t="inlineStr">
         <is>
-          <t>электродуга летний 17 078 / зимний 36 312 ₽ (дороже НМЦК!), термобельё 2 906, ботинки 2 438, каска 307; маржа держится на мелких СИЗ</t>
+          <t>30 000 шт × 10.0 ₽ (K3ЭДТА); доплата за дальнюю доставку 0 ₽ (МиниМед  прайс ©2026  РФ — импорт запрещён ПП 1875)</t>
         </is>
       </c>
       <c r="Q11" s="5" t="inlineStr"/>
       <c r="R11" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616452870</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0325300007726000124</t>
         </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>https://corp.roseltorg.ru/#notice/836575</t>
+          <t>http://roseltorg.ru</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1321,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>22.10.2026 05:00</t>
+          <t>21.10.2026 09:00</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -1323,64 +1331,64 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>0352500002526000085</t>
+          <t>32616452870</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>БУ Омской обл. «Тевризское ДРСУ»</t>
+          <t>ГУП РБ «Салаватводоканал» (2-й лот)</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Спецодежда и обувь зимняя</t>
+          <t>Костюмы от электродуги, термобельё, обувь, СИЗ (9 позиций)</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · запрос котировок</t>
+          <t>223-ФЗ · запрос котировок (МСП)</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>Росэлторг (corp)</t>
         </is>
       </c>
       <c r="I12" s="7" t="n">
-        <v>498744.79</v>
+        <v>700000</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>385360</v>
+        <v>558596</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>0.2273402996350097</v>
+        <v>0.2020057142857142</v>
       </c>
       <c r="L12" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>448870.311</v>
+        <v>630000</v>
       </c>
       <c r="N12" s="7" t="n">
-        <v>40162.48185163835</v>
+        <v>40799.32</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>0.1955018033649985</v>
+        <v>0.169123271889401</v>
       </c>
       <c r="P12" s="5" t="inlineStr">
         <is>
-          <t>Костюм для защиты от понижен 32×5 000 ₽; Костюм для защиты от понижен 11×5 000 ₽; Ботинки утепленные 55×2 618 ₽; Костюм сварщика зимний 3×5 990 ₽</t>
+          <t>электродуга летний 17 078 / зимний 36 312 ₽ (дороже НМЦК!), термобельё 2 906, ботинки 2 438, каска 307; маржа держится на мелких СИЗ</t>
         </is>
       </c>
       <c r="Q12" s="5" t="inlineStr"/>
       <c r="R12" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0352500002526000085</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616452870</t>
         </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>http://www.rts-tender.ru</t>
+          <t>https://corp.roseltorg.ru/#notice/836575</t>
         </is>
       </c>
     </row>
@@ -1390,27 +1398,27 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>26.10.2026 08:00</t>
+          <t>22.10.2026 05:00</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Пробирки</t>
+          <t>Спецодежда</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>0325300007726000124</t>
+          <t>0352500002526000085</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>ГБУЗ АО «Городская поликлиника №5», Астрахань</t>
+          <t>БУ Омской обл. «Тевризское ДРСУ»</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные K3ЭДТА, 30 000 шт</t>
+          <t>Спецодежда и обувь зимняя</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1420,44 +1428,44 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Росэлторг</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="I13" s="7" t="n">
-        <v>496200</v>
+        <v>498744.79</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>318000</v>
+        <v>385360</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>0.3591293833131801</v>
+        <v>0.2273402996350097</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>372150</v>
+        <v>448870.311</v>
       </c>
       <c r="N13" s="7" t="n">
-        <v>34610.30465753425</v>
+        <v>40162.48185163835</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>0.3327214358955725</v>
+        <v>0.1955018033649985</v>
       </c>
       <c r="P13" s="5" t="inlineStr">
         <is>
-          <t>30 000 шт × 9.9 ₽ (K3ЭДТА); доставка 21 000 ₽</t>
+          <t>Костюм для защиты от понижен 32×5 000 ₽; Костюм для защиты от понижен 11×5 000 ₽; Ботинки утепленные 55×2 618 ₽; Костюм сварщика зимний 3×5 990 ₽</t>
         </is>
       </c>
       <c r="Q13" s="5" t="inlineStr"/>
       <c r="R13" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0325300007726000124</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0352500002526000085</t>
         </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>http://roseltorg.ru</t>
+          <t>http://www.rts-tender.ru</t>
         </is>
       </c>
     </row>
@@ -1555,13 +1563,13 @@
         <v>112355537.37</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>56810847.5</v>
+        <v>56856615</v>
       </c>
       <c r="K15" s="13" t="n"/>
       <c r="L15" s="13" t="n"/>
       <c r="M15" s="13" t="n"/>
       <c r="N15" s="12" t="n">
-        <v>29143362.37535377</v>
+        <v>29103181.01816199</v>
       </c>
       <c r="O15" s="13" t="n"/>
       <c r="P15" s="13" t="n"/>

--- a/GO_LIST_2010.xlsx
+++ b/GO_LIST_2010.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -770,74 +770,74 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>21.10.2026 09:00</t>
+          <t>30.10.2026 12:00</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Спецодежда</t>
+          <t>Форма</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>32616453117</t>
+          <t>B1510261835045</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>ГУП РБ «Салаватводоканал»</t>
+          <t>АНО «Таврида.Арт», Судак</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Спецодежда зимняя, КЩС, сварщика, сигнальная (11 позиций)</t>
+          <t>Форменная одежда СБ: 8 позиций, 145 комплектов (по ТЗ)</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ · запрос предложений (МСП)</t>
+          <t>Коммерческий тендер</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Росэлторг (corp)</t>
+          <t>Росэлторг (коммерч.)</t>
         </is>
       </c>
       <c r="I5" s="7" t="n">
-        <v>1500000</v>
+        <v>4169750</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>681523</v>
+        <v>2925900</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>0.5456513333333333</v>
+        <v>0.2983032555908628</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="N5" s="9" t="n">
-        <v>539980.1497260274</v>
+        <v>3752775</v>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>595560.0032876713</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>0.5269292771394903</v>
+        <v>0.2693888846601725</v>
       </c>
       <c r="P5" s="5" t="inlineStr">
         <is>
-          <t>по позициям: зимний костюм 5 091 ₽, куртка 2 551, брюки/п/к 1 225, КЩС 4 783, сварщик 5 990, сигнальный 6 893 (прайсы 2026 + доставка)</t>
-        </is>
-      </c>
-      <c r="Q5" s="5" t="inlineStr"/>
-      <c r="R5" s="10" t="inlineStr">
-        <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616453117</t>
-        </is>
-      </c>
+          <t>по ТЗ: костюм 3 350, кофта 2 300, куртка 3 500, шапка 550, полуботинки 2 900, жилет 4 500, перчатки 1 500, снуд 420 ₽ + доставка в Судак 120 тыс.</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>поставка 10 дней — нужен товар в наличии; оплата 30 дн. после приёмки; цены кофты, ботинок, жилета, перчаток — подтвердить КП</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr"/>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>https://corp.roseltorg.ru/#notice/835021</t>
+          <t>https://www.roseltorg.ru/procedures/search?query_field=B1510261835045</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>21.10.2026 09:00</t>
+          <t>22.10.2026 05:00</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -1331,64 +1331,64 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>32616452870</t>
+          <t>0352500002526000085</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>ГУП РБ «Салаватводоканал» (2-й лот)</t>
+          <t>БУ Омской обл. «Тевризское ДРСУ»</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Костюмы от электродуги, термобельё, обувь, СИЗ (9 позиций)</t>
+          <t>Спецодежда и обувь зимняя</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ · запрос котировок (МСП)</t>
+          <t>44-ФЗ · запрос котировок</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>Росэлторг (corp)</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="I12" s="7" t="n">
-        <v>700000</v>
+        <v>498744.79</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>558596</v>
+        <v>385360</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>0.2020057142857142</v>
+        <v>0.2273402996350097</v>
       </c>
       <c r="L12" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>630000</v>
+        <v>448870.311</v>
       </c>
       <c r="N12" s="7" t="n">
-        <v>40799.32</v>
+        <v>40162.48185163835</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>0.169123271889401</v>
+        <v>0.1955018033649985</v>
       </c>
       <c r="P12" s="5" t="inlineStr">
         <is>
-          <t>электродуга летний 17 078 / зимний 36 312 ₽ (дороже НМЦК!), термобельё 2 906, ботинки 2 438, каска 307; маржа держится на мелких СИЗ</t>
+          <t>Костюм для защиты от понижен 32×5 000 ₽; Костюм для защиты от понижен 11×5 000 ₽; Ботинки утепленные 55×2 618 ₽; Костюм сварщика зимний 3×5 990 ₽</t>
         </is>
       </c>
       <c r="Q12" s="5" t="inlineStr"/>
       <c r="R12" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616452870</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0352500002526000085</t>
         </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>https://corp.roseltorg.ru/#notice/836575</t>
+          <t>http://www.rts-tender.ru</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>22.10.2026 05:00</t>
+          <t>26.10.2026 05:00</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>0352500002526000085</t>
+          <t>0352500002526000089</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>БУ Омской обл. «Тевризское ДРСУ»</t>
+          <t>БУ Омской обл. (Большереченское ДРСУ)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1432,35 +1432,35 @@
         </is>
       </c>
       <c r="I13" s="7" t="n">
-        <v>498744.79</v>
+        <v>498211.82</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>385360</v>
+        <v>399136</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>0.2273402996350097</v>
+        <v>0.1988628451247905</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>448870.311</v>
+        <v>448390.638</v>
       </c>
       <c r="N13" s="7" t="n">
-        <v>40162.48185163835</v>
+        <v>27663.44842735345</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>0.1955018033649985</v>
+        <v>0.1658508965202331</v>
       </c>
       <c r="P13" s="5" t="inlineStr">
         <is>
-          <t>Костюм для защиты от понижен 32×5 000 ₽; Костюм для защиты от понижен 11×5 000 ₽; Ботинки утепленные 55×2 618 ₽; Костюм сварщика зимний 3×5 990 ₽</t>
+          <t>Костюм для защиты от понижен 44×5 000 ₽; Костюм для защиты от понижен 5×5 000 ₽; Ботинки утепленные 51×2 618 ₽; Костюм сварщика зимний 2×5 990 ₽</t>
         </is>
       </c>
       <c r="Q13" s="5" t="inlineStr"/>
       <c r="R13" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0352500002526000085</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0352500002526000089</t>
         </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
@@ -1470,119 +1470,67 @@
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>26.10.2026 05:00</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Спецодежда</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>0352500002526000089</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>БУ Омской обл. (Большереченское ДРСУ)</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Спецодежда и обувь зимняя</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>44-ФЗ · запрос котировок</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>РТС-тендер</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="n">
-        <v>498211.82</v>
-      </c>
-      <c r="J14" s="7" t="n">
-        <v>399136</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>0.1988628451247905</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M14" s="7" t="n">
-        <v>448390.638</v>
-      </c>
-      <c r="N14" s="7" t="n">
-        <v>27663.44842735345</v>
-      </c>
-      <c r="O14" s="8" t="n">
-        <v>0.1658508965202331</v>
-      </c>
-      <c r="P14" s="5" t="inlineStr">
-        <is>
-          <t>Костюм для защиты от понижен 44×5 000 ₽; Костюм для защиты от понижен 5×5 000 ₽; Ботинки утепленные 51×2 618 ₽; Костюм сварщика зимний 2×5 990 ₽</t>
-        </is>
-      </c>
-      <c r="Q14" s="5" t="inlineStr"/>
-      <c r="R14" s="10" t="inlineStr">
-        <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0352500002526000089</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>http://www.rts-tender.ru</t>
-        </is>
-      </c>
+      <c r="A14" s="11" t="inlineStr"/>
+      <c r="B14" s="11" t="inlineStr"/>
+      <c r="C14" s="11" t="inlineStr"/>
+      <c r="D14" s="11" t="inlineStr"/>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>ИТОГО по подтверждённым</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr"/>
+      <c r="G14" s="11" t="inlineStr"/>
+      <c r="H14" s="11" t="inlineStr"/>
+      <c r="I14" s="12" t="n">
+        <v>114325287.37</v>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>58542396</v>
+      </c>
+      <c r="K14" s="13" t="n"/>
+      <c r="L14" s="13" t="n"/>
+      <c r="M14" s="13" t="n"/>
+      <c r="N14" s="12" t="n">
+        <v>29117961.55172363</v>
+      </c>
+      <c r="O14" s="13" t="n"/>
+      <c r="P14" s="13" t="n"/>
+      <c r="Q14" s="13" t="n"/>
+      <c r="R14" s="13" t="n"/>
+      <c r="S14" s="13" t="n"/>
     </row>
     <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="11" t="inlineStr"/>
-      <c r="B15" s="11" t="inlineStr"/>
-      <c r="C15" s="11" t="inlineStr"/>
-      <c r="D15" s="11" t="inlineStr"/>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>ИТОГО по подтверждённым</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr"/>
-      <c r="G15" s="11" t="inlineStr"/>
-      <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="12" t="n">
-        <v>112355537.37</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>56856615</v>
-      </c>
-      <c r="K15" s="13" t="n"/>
-      <c r="L15" s="13" t="n"/>
-      <c r="M15" s="13" t="n"/>
-      <c r="N15" s="12" t="n">
-        <v>29103181.01816199</v>
-      </c>
-      <c r="O15" s="13" t="n"/>
-      <c r="P15" s="13" t="n"/>
-      <c r="Q15" s="13" t="n"/>
-      <c r="R15" s="13" t="n"/>
-      <c r="S15" s="13" t="n"/>
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n"/>
+      <c r="P15" s="2" t="n"/>
+      <c r="Q15" s="2" t="n"/>
+      <c r="R15" s="2" t="n"/>
+      <c r="S15" s="2" t="n"/>
     </row>
     <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
+      <c r="A16" s="14" t="inlineStr"/>
+      <c r="B16" s="14" t="inlineStr"/>
+      <c r="C16" s="14" t="inlineStr"/>
+      <c r="D16" s="14" t="inlineStr"/>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Перспективные — только оценка, нужна спецификация</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="n"/>
@@ -1599,29 +1547,81 @@
       <c r="S16" s="2" t="n"/>
     </row>
     <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="14" t="inlineStr"/>
-      <c r="B17" s="14" t="inlineStr"/>
-      <c r="C17" s="14" t="inlineStr"/>
-      <c r="D17" s="14" t="inlineStr"/>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Перспективные — только оценка, нужна спецификация</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-      <c r="O17" s="2" t="n"/>
-      <c r="P17" s="2" t="n"/>
-      <c r="Q17" s="2" t="n"/>
-      <c r="R17" s="2" t="n"/>
-      <c r="S17" s="2" t="n"/>
+      <c r="A17" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>26.10.2026 17:40</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Обувь</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>386-076</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>ООО «Союзспецодежда»</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>Ботинки с высокими берцами, 4 000 пар</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="inlineStr">
+        <is>
+          <t>Коммерческий тендер</t>
+        </is>
+      </c>
+      <c r="H17" s="16" t="inlineStr">
+        <is>
+          <t>Bidzaar</t>
+        </is>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>10800000</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>9600000</v>
+      </c>
+      <c r="K17" s="19" t="n">
+        <v>0.1111111111111112</v>
+      </c>
+      <c r="L17" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="18" t="n">
+        <v>10800000</v>
+      </c>
+      <c r="N17" s="18" t="n">
+        <v>678286.0273972603</v>
+      </c>
+      <c r="O17" s="19" t="n">
+        <v>0.07448323268031626</v>
+      </c>
+      <c r="P17" s="16" t="inlineStr">
+        <is>
+          <t>оценка: 2 400 ₽/пара (Спецобъединение/Тракт 2026); НМЦК нет — сумма = наше КП</t>
+        </is>
+      </c>
+      <c r="Q17" s="16" t="inlineStr">
+        <is>
+          <t>оценка — нужна спецификация</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="inlineStr"/>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>https://bidzaar.com/</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="15" t="n">
@@ -1629,63 +1629,63 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>30.10.2026 12:00</t>
+          <t>26.10.2026 13:00</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>Форма</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>B1510261835045</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="E18" s="16" t="inlineStr">
         <is>
-          <t>АНО «Таврида.Арт», Судак</t>
+          <t>ООО «РМЗ», Салават</t>
         </is>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>Форменная одежда службы безопасности</t>
+          <t>Затворы дисковые</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
         <is>
-          <t>Коммерческий тендер</t>
+          <t>Коммерческий · конкурентный отбор</t>
         </is>
       </c>
       <c r="H18" s="16" t="inlineStr">
         <is>
-          <t>Росэлторг (коммерч.)</t>
+          <t>ЭТП «Торги РФ»</t>
         </is>
       </c>
       <c r="I18" s="18" t="n">
-        <v>4169750</v>
+        <v>10474222</v>
       </c>
       <c r="J18" s="18" t="n">
-        <v>2818752</v>
+        <v>8414990</v>
       </c>
       <c r="K18" s="19" t="n">
-        <v>0.3239997601774687</v>
+        <v>0.1965999956846437</v>
       </c>
       <c r="L18" s="19" t="n">
         <v>0.1</v>
       </c>
       <c r="M18" s="18" t="n">
-        <v>3752775</v>
+        <v>9426799.800000001</v>
       </c>
       <c r="N18" s="18" t="n">
-        <v>689630.0761643836</v>
+        <v>560777.4667024664</v>
       </c>
       <c r="O18" s="19" t="n">
-        <v>0.2961442487486347</v>
+        <v>0.1634948032841103</v>
       </c>
       <c r="P18" s="16" t="inlineStr">
         <is>
-          <t>оценка по правилу 3 500 / 5 000 ₽ за комплект; позиции не видны</t>
+          <t>оценка по категории (~20% маржа), спецификация на площадке</t>
         </is>
       </c>
       <c r="Q18" s="16" t="inlineStr">
@@ -1696,7 +1696,7 @@
       <c r="R18" s="5" t="inlineStr"/>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>https://www.roseltorg.ru/procedures/search?query_field=B1510261835045</t>
+          <t>https://торги.рф/</t>
         </is>
       </c>
     </row>
@@ -1706,63 +1706,63 @@
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>26.10.2026 17:40</t>
+          <t>26.10.2026 13:00</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>Обувь</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>386-076</t>
+          <t>8002</t>
         </is>
       </c>
       <c r="E19" s="16" t="inlineStr">
         <is>
-          <t>ООО «Союзспецодежда»</t>
+          <t>ООО «РМЗ», Салават</t>
         </is>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
-          <t>Ботинки с высокими берцами, 4 000 пар</t>
+          <t>Запорная арматура</t>
         </is>
       </c>
       <c r="G19" s="16" t="inlineStr">
         <is>
-          <t>Коммерческий тендер</t>
+          <t>Коммерческий · конкурентный отбор</t>
         </is>
       </c>
       <c r="H19" s="16" t="inlineStr">
         <is>
-          <t>Bidzaar</t>
+          <t>ЭТП «Торги РФ»</t>
         </is>
       </c>
       <c r="I19" s="18" t="n">
-        <v>10800000</v>
+        <v>4248523</v>
       </c>
       <c r="J19" s="18" t="n">
-        <v>9600000</v>
+        <v>3413263</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>0.1111111111111112</v>
+        <v>0.196600089019172</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M19" s="18" t="n">
-        <v>10800000</v>
+        <v>3823670.7</v>
       </c>
       <c r="N19" s="18" t="n">
-        <v>678286.0273972603</v>
+        <v>227461.2483495892</v>
       </c>
       <c r="O19" s="19" t="n">
-        <v>0.07448323268031626</v>
+        <v>0.1634949004646152</v>
       </c>
       <c r="P19" s="16" t="inlineStr">
         <is>
-          <t>оценка: 2 400 ₽/пара (Спецобъединение/Тракт 2026); НМЦК нет — сумма = наше КП</t>
+          <t>оценка по категории</t>
         </is>
       </c>
       <c r="Q19" s="16" t="inlineStr">
@@ -1772,160 +1772,6 @@
       </c>
       <c r="R19" s="5" t="inlineStr"/>
       <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>https://bidzaar.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>26.10.2026 13:00</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>Арматура</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>8004</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>ООО «РМЗ», Салават</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>Затворы дисковые</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>Коммерческий · конкурентный отбор</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>ЭТП «Торги РФ»</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="n">
-        <v>10474222</v>
-      </c>
-      <c r="J20" s="18" t="n">
-        <v>8414990</v>
-      </c>
-      <c r="K20" s="19" t="n">
-        <v>0.1965999956846437</v>
-      </c>
-      <c r="L20" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M20" s="18" t="n">
-        <v>9426799.800000001</v>
-      </c>
-      <c r="N20" s="18" t="n">
-        <v>560777.4667024664</v>
-      </c>
-      <c r="O20" s="19" t="n">
-        <v>0.1634948032841103</v>
-      </c>
-      <c r="P20" s="16" t="inlineStr">
-        <is>
-          <t>оценка по категории (~20% маржа), спецификация на площадке</t>
-        </is>
-      </c>
-      <c r="Q20" s="16" t="inlineStr">
-        <is>
-          <t>оценка — нужна спецификация</t>
-        </is>
-      </c>
-      <c r="R20" s="5" t="inlineStr"/>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>https://торги.рф/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>26.10.2026 13:00</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Арматура</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>8002</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>ООО «РМЗ», Салават</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>Запорная арматура</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>Коммерческий · конкурентный отбор</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>ЭТП «Торги РФ»</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="n">
-        <v>4248523</v>
-      </c>
-      <c r="J21" s="18" t="n">
-        <v>3413263</v>
-      </c>
-      <c r="K21" s="19" t="n">
-        <v>0.196600089019172</v>
-      </c>
-      <c r="L21" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M21" s="18" t="n">
-        <v>3823670.7</v>
-      </c>
-      <c r="N21" s="18" t="n">
-        <v>227461.2483495892</v>
-      </c>
-      <c r="O21" s="19" t="n">
-        <v>0.1634949004646152</v>
-      </c>
-      <c r="P21" s="16" t="inlineStr">
-        <is>
-          <t>оценка по категории</t>
-        </is>
-      </c>
-      <c r="Q21" s="16" t="inlineStr">
-        <is>
-          <t>оценка — нужна спецификация</t>
-        </is>
-      </c>
-      <c r="R21" s="5" t="inlineStr"/>
-      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>https://торги.рф/</t>
         </is>
@@ -1934,30 +1780,26 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/GO_LIST_2010.xlsx
+++ b/GO_LIST_2010.xlsx
@@ -770,74 +770,78 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>30.10.2026 12:00</t>
+          <t>23.10.2026 04:00</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Форма</t>
+          <t>Пробирки</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>B1510261835045</t>
+          <t>0338200002226000430</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>АНО «Таврида.Арт», Судак</t>
+          <t>ГБУЗ «Камчатский краевой онкологический диспансер»</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Форменная одежда СБ: 8 позиций, 145 комплектов (по ТЗ)</t>
+          <t>Пробирки вакуумные, 82 200 шт</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Коммерческий тендер</t>
+          <t>44-ФЗ · запрос котировок</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Росэлторг (коммерч.)</t>
+          <t>Росэлторг</t>
         </is>
       </c>
       <c r="I5" s="7" t="n">
-        <v>4169750</v>
+        <v>2221608</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>2925900</v>
+        <v>1114900</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>0.2983032555908628</v>
+        <v>0.4981562903986662</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>3752775</v>
-      </c>
-      <c r="N5" s="7" t="n">
-        <v>595560.0032876713</v>
+        <v>1666206</v>
+      </c>
+      <c r="N5" s="9" t="n">
+        <v>426123.7896109588</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>0.2693888846601725</v>
+        <v>0.4774771362138123</v>
       </c>
       <c r="P5" s="5" t="inlineStr">
         <is>
-          <t>по ТЗ: костюм 3 350, кофта 2 300, куртка 3 500, шапка 550, полуботинки 2 900, жилет 4 500, перчатки 1 500, снуд 420 ₽ + доставка в Судак 120 тыс.</t>
+          <t>15 000 шт × 10.0 ₽ (натрия цитратом); 200 шт × 13.5 ₽ (лития гепарином); 24 000 шт × 15.0 ₽ (активатором свертывани); 22 000 шт × 10.0 ₽ (K2ЭДТА); доплата за дальнюю доставку 82 200 ₽ (МиниМед  прайс ©2026  РФ — импорт запрещён ПП 1875)</t>
         </is>
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>поставка 10 дней — нужен товар в наличии; оплата 30 дн. после приёмки; цены кофты, ботинок, жилета, перчаток — подтвердить КП</t>
-        </is>
-      </c>
-      <c r="R5" s="5" t="inlineStr"/>
+          <t>активатор посчитан с гелем (15 ₽) — с запасом; нужны РУ и реестр РФ (импорт запрещён)</t>
+        </is>
+      </c>
+      <c r="R5" s="10" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0338200002226000430</t>
+        </is>
+      </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>https://www.roseltorg.ru/procedures/search?query_field=B1510261835045</t>
+          <t>http://roseltorg.ru</t>
         </is>
       </c>
     </row>
@@ -847,78 +851,74 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>23.10.2026 04:00</t>
+          <t>26.10.2026 10:00</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Пробирки</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>0338200002226000430</t>
+          <t>32616480814</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>ГБУЗ «Камчатский краевой онкологический диспансер»</t>
+          <t>АО «Петербургский нефтяной терминал»</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные, 82 200 шт</t>
+          <t>Задвижки 30с41нж/30с941нж, 70 шт</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · запрос котировок</t>
+          <t>223-ФЗ · конкурентный отбор</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Росэлторг</t>
+          <t>ZakazRF (АГЗРТ)</t>
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>2221608</v>
+        <v>3163250.24</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>1114900</v>
+        <v>2107397</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>0.4981562903986662</v>
+        <v>0.3337874527435427</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>1666206</v>
+        <v>2688762.704</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>426123.7896109588</v>
+        <v>416985.6198210191</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>0.4774771362138123</v>
+        <v>0.3063352565298155</v>
       </c>
       <c r="P6" s="5" t="inlineStr">
         <is>
-          <t>15 000 шт × 10.0 ₽ (натрия цитратом); 200 шт × 13.5 ₽ (лития гепарином); 24 000 шт × 15.0 ₽ (активатором свертывани); 22 000 шт × 10.0 ₽ (K2ЭДТА); доплата за дальнюю доставку 82 200 ₽ (МиниМед  прайс ©2026  РФ — импорт запрещён ПП 1875)</t>
-        </is>
-      </c>
-      <c r="Q6" s="5" t="inlineStr">
-        <is>
-          <t>активатор посчитан с гелем (15 ₽) — с запасом; нужны РУ и реестр РФ (импорт запрещён)</t>
-        </is>
-      </c>
+          <t>СибЗТА прайс 2026; 11 задвижек с электроприводом по 90 тыс. (если без приводов — себес ~1,1 млн)</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0338200002226000430</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616480814</t>
         </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>http://roseltorg.ru</t>
+          <t>https://223etp.zakazrf.ru/NotificationEX/id/509007</t>
         </is>
       </c>
     </row>
@@ -928,74 +928,74 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>26.10.2026 10:00</t>
+          <t>30.10.2026 12:00</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Форма</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>32616480814</t>
+          <t>B1510261835045</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>АО «Петербургский нефтяной терминал»</t>
+          <t>АНО «Таврида.Арт», Судак</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Задвижки 30с41нж/30с941нж, 70 шт</t>
+          <t>Форменная одежда СБ: 8 позиций, 145 комплектов (по ТЗ)</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ · конкурентный отбор</t>
+          <t>Коммерческий тендер</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>ZakazRF (АГЗРТ)</t>
+          <t>Росэлторг (коммерч.)</t>
         </is>
       </c>
       <c r="I7" s="7" t="n">
-        <v>3163250.24</v>
+        <v>4169750</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>2107397</v>
+        <v>3440900</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>0.3337874527435427</v>
+        <v>0.1747946519575514</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>2688762.704</v>
-      </c>
-      <c r="N7" s="9" t="n">
-        <v>416985.6198210191</v>
+        <v>3961262.5</v>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>319214.8824657535</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>0.3063352565298155</v>
+        <v>0.1407909406429432</v>
       </c>
       <c r="P7" s="5" t="inlineStr">
         <is>
-          <t>СибЗТА прайс 2026; 11 задвижек с электроприводом по 90 тыс. (если без приводов — себес ~1,1 млн)</t>
-        </is>
-      </c>
-      <c r="Q7" s="5" t="inlineStr"/>
-      <c r="R7" s="10" t="inlineStr">
-        <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616480814</t>
-        </is>
-      </c>
+          <t>построчная проверка 20.10: костюм 3 350, кофта 3 300, куртка 4 500, шапка 650, полуботинки 3 500, жилет 5 000, перчатки 1 800, снуд 420 ₽ + доставка 120 тыс.</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>поставка 10 дней — нужен товар в наличии; оплата 30 дн. после приёмки; цены кофты, ботинок, жилета, перчаток — подтвердить КП</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="inlineStr"/>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>https://223etp.zakazrf.ru/NotificationEX/id/509007</t>
+          <t>https://www.roseltorg.ru/procedures/search?query_field=B1510261835045</t>
         </is>
       </c>
     </row>
@@ -1486,13 +1486,13 @@
         <v>114325287.37</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>58542396</v>
+        <v>59057396</v>
       </c>
       <c r="K14" s="13" t="n"/>
       <c r="L14" s="13" t="n"/>
       <c r="M14" s="13" t="n"/>
       <c r="N14" s="12" t="n">
-        <v>29117961.55172363</v>
+        <v>28841616.43090171</v>
       </c>
       <c r="O14" s="13" t="n"/>
       <c r="P14" s="13" t="n"/>
@@ -1780,10 +1780,10 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId8"/>

--- a/GO_LIST_2010.xlsx
+++ b/GO_LIST_2010.xlsx
@@ -730,10 +730,10 @@
         <v>101102908</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>49931509</v>
+        <v>54810725</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>0.506131821648493</v>
+        <v>0.4578719239213179</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>0.15</v>
@@ -742,14 +742,14 @@
         <v>85937471.8</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>27230001.01395177</v>
+        <v>22809966.02655452</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>0.469413606444056</v>
+        <v>0.4175656716896615</v>
       </c>
       <c r="P4" s="5" t="inlineStr">
         <is>
-          <t>315 позиций по ценам 2026 (252 с ценой поставщика, 63 оценки), торг −10%, доставка 55 ₽/кг</t>
+          <t>построчная сверка 315 позиций с 2–3 источниками 2026 (20.10), торг −10%, доставка 55 ₽/кг</t>
         </is>
       </c>
       <c r="Q4" s="5" t="inlineStr">
@@ -1486,13 +1486,13 @@
         <v>114325287.37</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>59057396</v>
+        <v>63936612</v>
       </c>
       <c r="K14" s="13" t="n"/>
       <c r="L14" s="13" t="n"/>
       <c r="M14" s="13" t="n"/>
       <c r="N14" s="12" t="n">
-        <v>28841616.43090171</v>
+        <v>24421581.44350446</v>
       </c>
       <c r="O14" s="13" t="n"/>
       <c r="P14" s="13" t="n"/>
